--- a/survey_measurements_list.xlsx
+++ b/survey_measurements_list.xlsx
@@ -5,16 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ren\Documents\scripts and notes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ren\Documents\scripts and notes\trans standard sizing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305C56AF-F6BA-485F-A972-6D931E72E88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38461BF1-39BF-458C-9EB1-FBACC6EFFDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10104" yWindow="696" windowWidth="18444" windowHeight="11424" xr2:uid="{8E6E4257-9F92-425B-B108-F42EF46C1FAC}"/>
+    <workbookView xWindow="2052" yWindow="372" windowWidth="18444" windowHeight="11424" xr2:uid="{8E6E4257-9F92-425B-B108-F42EF46C1FAC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Measurements" sheetId="1" r:id="rId1"/>
+    <sheet name="First Questions" sheetId="2" r:id="rId2"/>
+    <sheet name="Last Questions" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Measurements!$A$1:$J$100</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="173">
   <si>
     <t>Separate measurements:</t>
   </si>
@@ -216,21 +221,6 @@
     <t>Clavicle to natural waist (front)</t>
   </si>
   <si>
-    <r>
-      <t>Clavicle to natural waist (front) with ruler</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (recommended for transfemmes)</t>
-    </r>
-  </si>
-  <si>
     <t>Side seam to natural waist</t>
   </si>
   <si>
@@ -270,21 +260,6 @@
     <t>Front (low) waist</t>
   </si>
   <si>
-    <r>
-      <t>Natural waist to high hip/low waist (front)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (required for transmascs)</t>
-    </r>
-  </si>
-  <si>
     <t>Natural waist to high hip/low waist (side)</t>
   </si>
   <si>
@@ -346,6 +321,234 @@
   </si>
   <si>
     <t>Ankle to floor</t>
+  </si>
+  <si>
+    <t>Natural waist to high hip/low waist (front)</t>
+  </si>
+  <si>
+    <t>Clavicle to natural waist (front) with ruler</t>
+  </si>
+  <si>
+    <t>Transmascs:</t>
+  </si>
+  <si>
+    <t>Transfemmes:</t>
+  </si>
+  <si>
+    <t>Mammoplasty?</t>
+  </si>
+  <si>
+    <t>Breast tissue removed?</t>
+  </si>
+  <si>
+    <t>Padded bra?</t>
+  </si>
+  <si>
+    <t>No extra crotch volume via surgery or tucking?</t>
+  </si>
+  <si>
+    <t>Extra crotch volume via surgery or packing?</t>
+  </si>
+  <si>
+    <t>Hysterectomy?</t>
+  </si>
+  <si>
+    <t>Any other surgery?</t>
+  </si>
+  <si>
+    <t>__if no, what?</t>
+  </si>
+  <si>
+    <t>____anything else</t>
+  </si>
+  <si>
+    <t>____no blockers or surgery</t>
+  </si>
+  <si>
+    <t>Standard dose T?</t>
+  </si>
+  <si>
+    <t>Standard dose E &amp; blockers or surgery?</t>
+  </si>
+  <si>
+    <t>____low dose E</t>
+  </si>
+  <si>
+    <t>____low dose T</t>
+  </si>
+  <si>
+    <t>Progesterone?</t>
+  </si>
+  <si>
+    <t>Consistently for 3 years?</t>
+  </si>
+  <si>
+    <t>__if no, how long?</t>
+  </si>
+  <si>
+    <t>____1-2 years</t>
+  </si>
+  <si>
+    <t>____&gt; 2 years</t>
+  </si>
+  <si>
+    <t>____&lt; 1 year</t>
+  </si>
+  <si>
+    <t>How long on HRT in total?</t>
+  </si>
+  <si>
+    <t>____3-5 years</t>
+  </si>
+  <si>
+    <t>____5-10 years</t>
+  </si>
+  <si>
+    <t>____10+ years</t>
+  </si>
+  <si>
+    <t>Muscular?</t>
+  </si>
+  <si>
+    <t>Age group? 18-20s, 30s, 40s, etc</t>
+  </si>
+  <si>
+    <t>Did you shop in birth sex aisle &amp; remember your size?</t>
+  </si>
+  <si>
+    <t>__Yes</t>
+  </si>
+  <si>
+    <t>__No, didn't shop there</t>
+  </si>
+  <si>
+    <t>__No, don't remember</t>
+  </si>
+  <si>
+    <t>___if yes:</t>
+  </si>
+  <si>
+    <t>____size 1</t>
+  </si>
+  <si>
+    <t>____sizing system 1</t>
+  </si>
+  <si>
+    <t>____sizing system 2</t>
+  </si>
+  <si>
+    <t>____size 2</t>
+  </si>
+  <si>
+    <t>____sizing system 3</t>
+  </si>
+  <si>
+    <t>____size 3</t>
+  </si>
+  <si>
+    <t>Plus size?</t>
+  </si>
+  <si>
+    <t>__pre-transition?</t>
+  </si>
+  <si>
+    <t>__now?</t>
+  </si>
+  <si>
+    <t>__by cis standards</t>
+  </si>
+  <si>
+    <t>__by trans standards?</t>
+  </si>
+  <si>
+    <t>Unusual Height? short/tall</t>
+  </si>
+  <si>
+    <t>How well did you fit standard sizing pre-transition?</t>
+  </si>
+  <si>
+    <t>__very well</t>
+  </si>
+  <si>
+    <t>__well with minor fit issues</t>
+  </si>
+  <si>
+    <t>__poorly (special sections worked well)</t>
+  </si>
+  <si>
+    <t>__poorly (special sections still had fit issues)</t>
+  </si>
+  <si>
+    <t>__poorly (needed but didn't use special section)</t>
+  </si>
+  <si>
+    <t>__very poorly (never had clothes without custom tailoring)</t>
+  </si>
+  <si>
+    <t>__N/A</t>
+  </si>
+  <si>
+    <t>How has transition &amp; new aisle changed that?</t>
+  </si>
+  <si>
+    <t>__for the better</t>
+  </si>
+  <si>
+    <t>__neutrally</t>
+  </si>
+  <si>
+    <t>__for the worse</t>
+  </si>
+  <si>
+    <t>Fit issues: too big/small</t>
+  </si>
+  <si>
+    <t>Anything else?</t>
+  </si>
+  <si>
+    <t>__shoulder width</t>
+  </si>
+  <si>
+    <t>__sleeve circumference</t>
+  </si>
+  <si>
+    <t>__sleeve length</t>
+  </si>
+  <si>
+    <t>__chest width</t>
+  </si>
+  <si>
+    <t>__breast space (transfemmes only)</t>
+  </si>
+  <si>
+    <t>__waist size</t>
+  </si>
+  <si>
+    <t>__torso length</t>
+  </si>
+  <si>
+    <t>__hip width</t>
+  </si>
+  <si>
+    <t>__pant crotch fit</t>
+  </si>
+  <si>
+    <t>__leg circumference</t>
+  </si>
+  <si>
+    <t>__leg length</t>
+  </si>
+  <si>
+    <t>Suggestions</t>
+  </si>
+  <si>
+    <t>__suggestion 1</t>
+  </si>
+  <si>
+    <t>__suggestion 2</t>
+  </si>
+  <si>
+    <t>__suggestion 3</t>
   </si>
 </sst>
 </file>
@@ -374,22 +577,24 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="20"/>
+      <sz val="11"/>
       <color rgb="FF2F5496"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF2F5496"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF2F5496"/>
-      <name val="Arial"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -400,7 +605,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -429,6 +634,34 @@
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -436,6 +669,70 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -443,50 +740,123 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -801,251 +1171,409 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{782534F7-93A5-452D-8BFC-5FD1A6713939}">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.5546875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="44.5546875" style="1" customWidth="1"/>
+    <col min="2" max="14" width="4.5546875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+      <c r="H1"/>
+      <c r="I1"/>
+      <c r="J1"/>
+      <c r="K1"/>
+      <c r="L1"/>
+      <c r="M1"/>
+      <c r="N1"/>
+      <c r="O1" s="13"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" s="17"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="18"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" s="17"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="18"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B18" s="17"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="18"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" ht="24.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="15" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>47</v>
       </c>
@@ -1060,257 +1588,1273 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A51" s="8" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="7" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="7" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="8" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="9" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="9" t="s">
+      <c r="A60" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="9" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="7" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="9" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="9" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="9" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="9" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="9" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="9" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="7" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="9" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="9" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="9" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="7" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="9" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="9" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="11" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="9" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:1" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A79" s="9" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="9" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="9" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="11" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="9" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="9" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="9" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="9" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="9" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="11" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="9" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="9" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="11" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="9" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="9" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="9" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="11" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="9" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="9" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="9" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="7" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="9" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="10" t="s">
-        <v>98</v>
-      </c>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6B5C61C-2837-477E-9A6F-5373991C1B40}">
+  <dimension ref="A1:Z24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.21875" style="23" customWidth="1"/>
+    <col min="2" max="13" width="4.44140625" style="19" customWidth="1"/>
+    <col min="14" max="14" width="23.21875" style="23" customWidth="1"/>
+    <col min="15" max="26" width="4.44140625" style="19" customWidth="1"/>
+    <col min="27" max="16384" width="8.88671875" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="21"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="O2" s="26"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="O3" s="30"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="O4" s="21"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20"/>
+      <c r="Y4" s="20"/>
+      <c r="Z4" s="20"/>
+    </row>
+    <row r="5" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="O5" s="21"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="31"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A7" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="O7" s="21"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+    </row>
+    <row r="8" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="O8" s="21"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A9" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="O9" s="21"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A10" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="O10" s="21"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="O11" s="21"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A12" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="O12" s="21"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="O13" s="21"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="O14" s="21"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A15" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="O15" s="21"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A16" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="O16" s="21"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A17" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="O17" s="21"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="20"/>
+      <c r="Z17" s="20"/>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A18" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="O18" s="21"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A19" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="O19" s="21"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="20"/>
+      <c r="Z19" s="20"/>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A20" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="O20" s="21"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="O21" s="21"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="20"/>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A22" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="O22" s="21"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="20"/>
+      <c r="Z22" s="20"/>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A23" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="31"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="28"/>
+      <c r="W23" s="28"/>
+      <c r="X23" s="28"/>
+      <c r="Y23" s="28"/>
+      <c r="Z23" s="28"/>
+    </row>
+    <row r="24" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="O24" s="21"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CA897D1-976F-407B-8CB7-14CC3BEE1693}">
+  <dimension ref="A1:M47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="48.5546875" customWidth="1"/>
+    <col min="2" max="13" width="10.109375" style="10" customWidth="1"/>
+    <col min="14" max="15" width="10.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="33" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="34" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="34" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="34" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="34" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="34" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="34" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="36" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="34" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="34" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="34" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="34" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="34" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="34" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="34" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="34" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="34" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="34" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="34" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="34" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="36" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="34" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="34" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="34" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="34" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="34" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="34" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="34" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="34" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="34" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="34" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="34" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="37" t="s">
+        <v>172</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>